--- a/WorkBot/refactor-experimental/data/orders/Sysco/Sysco_Easthill_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Sysco/Sysco_Easthill_20251114.xlsx
@@ -454,20 +454,14 @@
           <t>Hash Brown</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>23.89</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>47.78</t>
-        </is>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.89</v>
+      </c>
+      <c r="E2" t="n">
+        <v>47.78</v>
       </c>
     </row>
     <row r="3">
@@ -481,20 +475,14 @@
           <t>Avocado - Halves Fresh</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>33.90</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>67.80</t>
-        </is>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>67.8</v>
       </c>
     </row>
     <row r="4">
@@ -508,20 +496,14 @@
           <t>Chobani - Mango</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>15.39</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>15.39</t>
-        </is>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="E4" t="n">
+        <v>15.39</v>
       </c>
     </row>
     <row r="5">
@@ -535,20 +517,14 @@
           <t>Naked - Berry Blast</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>24.24</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>24.24</t>
-        </is>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="E5" t="n">
+        <v>24.24</v>
       </c>
     </row>
     <row r="6">
@@ -562,20 +538,14 @@
           <t>PKT Hot Sauce - Franks</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>21.68</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>21.68</t>
-        </is>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>21.68</v>
+      </c>
+      <c r="E6" t="n">
+        <v>21.68</v>
       </c>
     </row>
     <row r="7">
@@ -589,20 +559,14 @@
           <t>Frz Orange Juice</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>104.13</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>104.13</t>
-        </is>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>104.13</v>
+      </c>
+      <c r="E7" t="n">
+        <v>104.13</v>
       </c>
     </row>
     <row r="8">
@@ -616,20 +580,14 @@
           <t>Smoothie Ice Cream</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>81.15</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>81.15</t>
-        </is>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>81.15000000000001</v>
+      </c>
+      <c r="E8" t="n">
+        <v>81.15000000000001</v>
       </c>
     </row>
   </sheetData>
